--- a/data/non_energy_use.xlsx
+++ b/data/non_energy_use.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usepa-my.sharepoint.com/personal/corra_joseph_epa_gov/Documents/Profile/Documents/Fossil Fuels/Fossil Fuels/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{79912791-07AC-4B3D-B0F1-18EAE875595E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{79912791-07AC-4B3D-B0F1-18EAE875595E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD6A612D-BD28-4764-A52D-D7951A0A7774}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{84BE4831-3B4C-4C56-A59B-3FAFE0010413}"/>
+    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{84BE4831-3B4C-4C56-A59B-3FAFE0010413}"/>
   </bookViews>
   <sheets>
     <sheet name="neu" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1" iterateDelta="1.0000000000000001E-5"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -447,10 +447,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB57B73F-4A8D-4E77-9C5B-64217D2C9456}">
-  <dimension ref="A1:AH20"/>
+  <dimension ref="A1:AI20"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="25.6328125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -553,8 +556,11 @@
       <c r="AH1">
         <v>2022</v>
       </c>
+      <c r="AI1">
+        <v>2023</v>
+      </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -646,19 +652,22 @@
         <v>5595.6761258353708</v>
       </c>
       <c r="AE2">
-        <v>5533.7941076188963</v>
+        <v>5533.9499768895475</v>
       </c>
       <c r="AF2">
-        <v>5492.7171791039245</v>
+        <v>5492.2481339561427</v>
       </c>
       <c r="AG2">
-        <v>5738.4099636624796</v>
+        <v>5738.0197868738669</v>
       </c>
       <c r="AH2">
-        <v>5734.392153251425</v>
+        <v>5715.1749791538114</v>
+      </c>
+      <c r="AI2">
+        <v>5874.2881284961886</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -750,19 +759,22 @@
         <v>124.67753407088412</v>
       </c>
       <c r="AE3">
-        <v>112.83747864130271</v>
+        <v>112.99334791195349</v>
       </c>
       <c r="AF3">
-        <v>79.875589997130135</v>
+        <v>79.406544849348563</v>
       </c>
       <c r="AG3">
-        <v>77.879517773454495</v>
+        <v>77.489340984841817</v>
       </c>
       <c r="AH3">
-        <v>46.673338451398934</v>
+        <v>46.361164353785398</v>
+      </c>
+      <c r="AI3">
+        <v>65.407498443247789</v>
       </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -865,8 +877,11 @@
       <c r="AH4">
         <v>9.4640446919181898</v>
       </c>
+      <c r="AI4">
+        <v>9.4581343063049435</v>
+      </c>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -967,10 +982,13 @@
         <v>731.45600000000002</v>
       </c>
       <c r="AH5">
+        <v>730.75199999999995</v>
+      </c>
+      <c r="AI5">
         <v>729.34399999999994</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1073,8 +1091,11 @@
       <c r="AH6">
         <v>916.13400000000001</v>
       </c>
+      <c r="AI6">
+        <v>891.75800000000004</v>
+      </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1175,10 +1196,13 @@
         <v>2865.7948280000001</v>
       </c>
       <c r="AH7">
-        <v>3026.5309999999999</v>
+        <v>3010.7539999999999</v>
+      </c>
+      <c r="AI7">
+        <v>3216.8109999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1279,10 +1303,13 @@
         <v>113.49299999999999</v>
       </c>
       <c r="AH8">
-        <v>119.544</v>
+        <v>115.008</v>
+      </c>
+      <c r="AI8">
+        <v>86.3</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1385,8 +1412,11 @@
       <c r="AH9">
         <v>0</v>
       </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1489,8 +1519,11 @@
       <c r="AH10">
         <v>265.51206400000001</v>
       </c>
+      <c r="AI10">
+        <v>271.84640000000002</v>
+      </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1593,8 +1626,11 @@
       <c r="AH11">
         <v>127.73396102500001</v>
       </c>
+      <c r="AI11">
+        <v>119.56621592499999</v>
+      </c>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1697,8 +1733,11 @@
       <c r="AH12">
         <v>157.07933803502155</v>
       </c>
+      <c r="AI12">
+        <v>155.79270399709844</v>
+      </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -1801,8 +1840,11 @@
       <c r="AH13">
         <v>44.971532344085873</v>
       </c>
+      <c r="AI13">
+        <v>47.653070491538259</v>
+      </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -1905,13 +1947,16 @@
       <c r="AH14">
         <v>89.153024000000002</v>
       </c>
+      <c r="AI14">
+        <v>89.242239999999995</v>
+      </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -2014,8 +2059,11 @@
       <c r="AH16">
         <v>5.8250000000000002</v>
       </c>
+      <c r="AI16">
+        <v>5.8250000000000002</v>
+      </c>
     </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -2118,8 +2166,11 @@
       <c r="AH17">
         <v>13.038350416</v>
       </c>
+      <c r="AI17">
+        <v>9.0449165170000008</v>
+      </c>
     </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -2222,8 +2273,11 @@
       <c r="AH18">
         <v>183.38850028799999</v>
       </c>
+      <c r="AI18">
+        <v>176.238948816</v>
+      </c>
     </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -2324,10 +2378,13 @@
         <v>119.03799999999998</v>
       </c>
       <c r="AH19">
-        <v>125.386</v>
+        <v>129.922</v>
+      </c>
+      <c r="AI19">
+        <v>97.492000000000004</v>
       </c>
     </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -2428,7 +2485,10 @@
         <v>119.03799999999998</v>
       </c>
       <c r="AH20">
-        <v>125.386</v>
+        <v>129.922</v>
+      </c>
+      <c r="AI20">
+        <v>97.492000000000004</v>
       </c>
     </row>
   </sheetData>

--- a/data/non_energy_use.xlsx
+++ b/data/non_energy_use.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usepa-my.sharepoint.com/personal/corra_joseph_epa_gov/Documents/Profile/Documents/Fossil Fuels/Fossil Fuels/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{79912791-07AC-4B3D-B0F1-18EAE875595E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD6A612D-BD28-4764-A52D-D7951A0A7774}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{79912791-07AC-4B3D-B0F1-18EAE875595E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE3BD0D0-8D83-4605-9C87-8CB76416029F}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{84BE4831-3B4C-4C56-A59B-3FAFE0010413}"/>
   </bookViews>

--- a/data/non_energy_use.xlsx
+++ b/data/non_energy_use.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usepa-my.sharepoint.com/personal/corra_joseph_epa_gov/Documents/Profile/Documents/Fossil Fuels/Fossil Fuels/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{79912791-07AC-4B3D-B0F1-18EAE875595E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE3BD0D0-8D83-4605-9C87-8CB76416029F}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{79912791-07AC-4B3D-B0F1-18EAE875595E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3F9C647-22AB-4E43-A972-322A3FACEEF1}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{84BE4831-3B4C-4C56-A59B-3FAFE0010413}"/>
   </bookViews>
@@ -1314,100 +1314,100 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>125.15810999999999</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>147.00839999999999</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>161.27265</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>166.14213000000001</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>169.36457999999999</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>168.96264000000002</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>177.49578</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>164.45814000000001</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>147.00609</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>182.48769000000001</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>171.57987</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>131.58914999999999</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>111.92180999999999</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>110.41800000000001</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>111.22188000000001</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>98.119559999999993</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>70.053060000000002</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>89.681129999999996</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>76.523370000000014</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>63.767550000000007</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>77.749979999999994</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>27.338850000000001</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>42.210630000000002</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>47.110140000000001</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>44.194920000000003</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>80.233230000000006</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>56.079870000000007</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>86.370900000000006</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>111.84558</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>166.62954000000002</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>176.46782999999999</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>217.11228</v>
       </c>
       <c r="AH9">
         <v>0</v>
